--- a/data/trans_orig/IP2901-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP2901-Clase-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12634</t>
+          <t>11964</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25130</t>
+          <t>24841</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8039</t>
+          <t>8128</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19067</t>
+          <t>18715</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>23126</t>
+          <t>23343</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39380</t>
+          <t>40333</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>20,47%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5086</t>
+          <t>5012</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14395</t>
+          <t>14069</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4087</t>
+          <t>4113</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13111</t>
+          <t>13262</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10397</t>
+          <t>11194</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>23480</t>
+          <t>22888</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,62%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>67044</t>
+          <t>66771</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>81225</t>
+          <t>81732</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>66,07%</t>
+          <t>65,8%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>80,05%</t>
+          <t>80,55%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>68253</t>
+          <t>67811</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>80306</t>
+          <t>80420</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>71,42%</t>
+          <t>70,95%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>84,03%</t>
+          <t>84,15%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>139609</t>
+          <t>139600</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>158513</t>
+          <t>158632</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>80,45%</t>
+          <t>80,51%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7893</t>
+          <t>7993</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>18238</t>
+          <t>18316</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10630</t>
+          <t>11418</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>22778</t>
+          <t>23504</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>21601</t>
+          <t>21226</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>36332</t>
+          <t>36947</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>21,39%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2794</t>
+          <t>2749</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11244</t>
+          <t>11148</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2607</t>
+          <t>2477</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10047</t>
+          <t>9601</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>6618</t>
+          <t>6879</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>17645</t>
+          <t>17667</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,23%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>62014</t>
+          <t>61198</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>74264</t>
+          <t>74007</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>71,47%</t>
+          <t>70,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>85,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>57362</t>
+          <t>57836</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>70420</t>
+          <t>70399</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>66,72%</t>
+          <t>67,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>81,91%</t>
+          <t>81,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>124179</t>
+          <t>124039</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>141600</t>
+          <t>140981</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>71,89%</t>
+          <t>71,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>81,97%</t>
+          <t>81,62%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5884</t>
+          <t>6269</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15452</t>
+          <t>15627</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>11651</t>
+          <t>10987</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>24125</t>
+          <t>23536</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>19640</t>
+          <t>20286</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>34501</t>
+          <t>36575</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>22,51%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2279</t>
+          <t>2245</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9470</t>
+          <t>8618</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2808</t>
+          <t>3137</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11061</t>
+          <t>11729</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6466</t>
+          <t>6915</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17349</t>
+          <t>17656</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,86%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>46324</t>
+          <t>45735</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>56814</t>
+          <t>56278</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,47%</t>
+          <t>68,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,2%</t>
+          <t>84,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>64914</t>
+          <t>65550</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>78795</t>
+          <t>78973</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,74%</t>
+          <t>68,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,22%</t>
+          <t>82,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>115184</t>
+          <t>114373</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>132979</t>
+          <t>132603</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,88%</t>
+          <t>70,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,82%</t>
+          <t>81,59%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29713</t>
+          <t>29545</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>46626</t>
+          <t>47738</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>28974</t>
+          <t>29032</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>45838</t>
+          <t>46743</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>63183</t>
+          <t>61806</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>88157</t>
+          <t>88089</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,33%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7580</t>
+          <t>7423</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18782</t>
+          <t>18571</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9593</t>
+          <t>10035</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>21477</t>
+          <t>22358</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>19697</t>
+          <t>19665</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>35626</t>
+          <t>36137</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,16%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>136439</t>
+          <t>136619</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>155907</t>
+          <t>156181</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>69,23%</t>
+          <t>69,32%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>79,11%</t>
+          <t>79,25%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>135413</t>
+          <t>134761</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>154586</t>
+          <t>154218</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>68,62%</t>
+          <t>68,29%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>78,34%</t>
+          <t>78,15%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>278493</t>
+          <t>276421</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>305764</t>
+          <t>305109</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>70,61%</t>
+          <t>70,09%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>77,52%</t>
+          <t>77,36%</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>13294</t>
+          <t>13912</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>25908</t>
+          <t>26239</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>20759</t>
+          <t>20687</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>36282</t>
+          <t>35359</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>38282</t>
+          <t>38371</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>57956</t>
+          <t>57769</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,34%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1161</t>
+          <t>1163</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6634</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5770</t>
+          <t>5596</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>15251</t>
+          <t>16175</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>7934</t>
+          <t>7620</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>19101</t>
+          <t>18822</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,26%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>73165</t>
+          <t>72812</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>86030</t>
+          <t>85845</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>71,7%</t>
+          <t>71,36%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>84,13%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>80355</t>
+          <t>80582</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>96598</t>
+          <t>96428</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>63,8%</t>
+          <t>63,99%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>76,7%</t>
+          <t>76,57%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>156749</t>
+          <t>156818</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>178070</t>
+          <t>179048</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>68,76%</t>
+          <t>68,79%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>78,11%</t>
+          <t>78,54%</t>
         </is>
       </c>
     </row>
@@ -3012,12 +3012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5484</t>
+          <t>5618</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>15186</t>
+          <t>15006</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3027,12 +3027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3047,12 +3047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>9133</t>
+          <t>8598</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>19852</t>
+          <t>19693</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3062,12 +3062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>16386</t>
+          <t>16962</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>30854</t>
+          <t>31976</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3097,12 +3097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>22,13%</t>
         </is>
       </c>
     </row>
@@ -3125,12 +3125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>533</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5409</t>
+          <t>5008</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3145,7 +3145,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3165,7 +3165,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5501</t>
+          <t>5769</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3195,12 +3195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>1346</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>7668</t>
+          <t>8208</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3210,12 +3210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,68%</t>
         </is>
       </c>
     </row>
@@ -3238,12 +3238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>55760</t>
+          <t>56112</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>66353</t>
+          <t>66203</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3253,12 +3253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>75,96%</t>
+          <t>76,44%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3273,12 +3273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>49368</t>
+          <t>49366</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>60425</t>
+          <t>60550</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3293,7 +3293,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>84,99%</t>
+          <t>85,17%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>108908</t>
+          <t>108494</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>124319</t>
+          <t>124160</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3323,12 +3323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>75,37%</t>
+          <t>75,08%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>85,92%</t>
         </is>
       </c>
     </row>
@@ -3468,12 +3468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>94008</t>
+          <t>93175</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>122334</t>
+          <t>122692</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3503,12 +3503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>109220</t>
+          <t>109684</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>142327</t>
+          <t>141406</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3518,12 +3518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3538,12 +3538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>211334</t>
+          <t>211459</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>258698</t>
+          <t>256717</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3553,12 +3553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>19,76%</t>
         </is>
       </c>
     </row>
@@ -3581,12 +3581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>28308</t>
+          <t>27558</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>46176</t>
+          <t>45888</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3596,12 +3596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3616,12 +3616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>35306</t>
+          <t>35592</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>57448</t>
+          <t>56806</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3631,12 +3631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3651,12 +3651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>68955</t>
+          <t>68676</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>96535</t>
+          <t>96869</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3666,12 +3666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,46%</t>
         </is>
       </c>
     </row>
@@ -3694,12 +3694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>464820</t>
+          <t>467276</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>499584</t>
+          <t>500294</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3709,12 +3709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>74,08%</t>
+          <t>74,47%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>79,62%</t>
+          <t>79,74%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3729,12 +3729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>483427</t>
+          <t>482272</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>519724</t>
+          <t>518114</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>71,97%</t>
+          <t>71,79%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>77,37%</t>
+          <t>77,13%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3764,12 +3764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>956536</t>
+          <t>956855</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1008043</t>
+          <t>1007621</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>73,63%</t>
+          <t>73,65%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>77,59%</t>
+          <t>77,56%</t>
         </is>
       </c>
     </row>
@@ -4158,12 +4158,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10098</t>
+          <t>9254</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22073</t>
+          <t>21523</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4173,12 +4173,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10837</t>
+          <t>10772</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23314</t>
+          <t>22315</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4208,12 +4208,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24199</t>
+          <t>24157</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>40351</t>
+          <t>40248</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4243,12 +4243,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,55%</t>
         </is>
       </c>
     </row>
@@ -4271,12 +4271,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2591</t>
+          <t>2768</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10691</t>
+          <t>10617</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4286,12 +4286,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4306,12 +4306,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8170</t>
+          <t>8200</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19680</t>
+          <t>19933</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4321,12 +4321,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4341,12 +4341,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>13264</t>
+          <t>12736</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>26660</t>
+          <t>26503</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4356,12 +4356,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,85%</t>
         </is>
       </c>
     </row>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>61013</t>
+          <t>61500</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>74399</t>
+          <t>75023</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4399,12 +4399,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>67,84%</t>
+          <t>68,38%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>82,73%</t>
+          <t>83,42%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4419,12 +4419,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>51184</t>
+          <t>52488</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>66024</t>
+          <t>66453</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>57,82%</t>
+          <t>59,3%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>74,59%</t>
+          <t>75,07%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4454,12 +4454,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>117319</t>
+          <t>118277</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>136341</t>
+          <t>137556</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>65,74%</t>
+          <t>66,28%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>76,4%</t>
+          <t>77,08%</t>
         </is>
       </c>
     </row>
@@ -4614,12 +4614,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12852</t>
+          <t>13148</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>25316</t>
+          <t>25731</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4629,12 +4629,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>21154</t>
+          <t>21027</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>35671</t>
+          <t>35986</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>37846</t>
+          <t>37139</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>56733</t>
+          <t>57436</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4699,12 +4699,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>30,72%</t>
         </is>
       </c>
     </row>
@@ -4727,12 +4727,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3500</t>
+          <t>3397</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12225</t>
+          <t>11698</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4742,12 +4742,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5160</t>
+          <t>5294</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14409</t>
+          <t>14714</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>9932</t>
+          <t>10586</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>22662</t>
+          <t>22919</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,26%</t>
         </is>
       </c>
     </row>
@@ -4840,12 +4840,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>59538</t>
+          <t>59859</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>73634</t>
+          <t>73865</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4855,12 +4855,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>63,84%</t>
+          <t>64,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>79,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>49052</t>
+          <t>48556</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>64418</t>
+          <t>64269</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>52,36%</t>
+          <t>51,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>68,76%</t>
+          <t>68,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>114012</t>
+          <t>113164</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>135013</t>
+          <t>134772</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>60,99%</t>
+          <t>60,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>72,22%</t>
+          <t>72,09%</t>
         </is>
       </c>
     </row>
@@ -5070,12 +5070,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14687</t>
+          <t>14551</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>27598</t>
+          <t>27852</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>15693</t>
+          <t>16194</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>29204</t>
+          <t>29561</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>33807</t>
+          <t>33924</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>52225</t>
+          <t>52509</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>30,95%</t>
         </is>
       </c>
     </row>
@@ -5183,12 +5183,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4080</t>
+          <t>3932</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13269</t>
+          <t>13075</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4085</t>
+          <t>4072</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13660</t>
+          <t>12945</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9253</t>
+          <t>9703</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>22750</t>
+          <t>22545</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,29%</t>
         </is>
       </c>
     </row>
@@ -5296,12 +5296,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>48954</t>
+          <t>48727</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>63326</t>
+          <t>63333</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>57,72%</t>
+          <t>57,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,67%</t>
+          <t>74,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>46875</t>
+          <t>47405</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>61855</t>
+          <t>62182</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>55,26%</t>
+          <t>55,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,92%</t>
+          <t>73,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>100847</t>
+          <t>100459</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>121253</t>
+          <t>121483</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5381,12 +5381,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>59,45%</t>
+          <t>59,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,48%</t>
+          <t>71,61%</t>
         </is>
       </c>
     </row>
@@ -5526,12 +5526,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>36432</t>
+          <t>36476</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>56507</t>
+          <t>56459</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5561,12 +5561,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>45775</t>
+          <t>45064</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>66774</t>
+          <t>66977</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5596,12 +5596,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>88504</t>
+          <t>87730</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>115728</t>
+          <t>115950</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>27,04%</t>
         </is>
       </c>
     </row>
@@ -5639,12 +5639,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11280</t>
+          <t>12042</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23876</t>
+          <t>24648</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5654,12 +5654,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6818</t>
+          <t>5965</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>18578</t>
+          <t>16956</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5689,12 +5689,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>20268</t>
+          <t>21399</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>38611</t>
+          <t>39165</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5724,12 +5724,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,13%</t>
         </is>
       </c>
     </row>
@@ -5752,12 +5752,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>129242</t>
+          <t>128612</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>150386</t>
+          <t>150713</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5767,12 +5767,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>63,53%</t>
+          <t>63,22%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>73,92%</t>
+          <t>74,08%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>147428</t>
+          <t>146560</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>168617</t>
+          <t>170236</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5802,12 +5802,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>65,42%</t>
+          <t>65,04%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>74,83%</t>
+          <t>75,55%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>282613</t>
+          <t>282793</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>313084</t>
+          <t>313385</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5837,12 +5837,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>65,91%</t>
+          <t>65,95%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>73,02%</t>
+          <t>73,09%</t>
         </is>
       </c>
     </row>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>25852</t>
+          <t>25780</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>42666</t>
+          <t>42499</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5997,12 +5997,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>28585</t>
+          <t>28671</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>45555</t>
+          <t>46043</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6032,12 +6032,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>58877</t>
+          <t>58911</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>82674</t>
+          <t>83215</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6067,12 +6067,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>28,74%</t>
         </is>
       </c>
     </row>
@@ -6095,12 +6095,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6720</t>
+          <t>6752</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>17145</t>
+          <t>17706</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6110,12 +6110,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6130,12 +6130,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5242</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>15601</t>
+          <t>15722</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6165,12 +6165,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>14556</t>
+          <t>14340</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>29744</t>
+          <t>30119</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6180,12 +6180,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,4%</t>
         </is>
       </c>
     </row>
@@ -6208,12 +6208,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>94899</t>
+          <t>94355</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>113334</t>
+          <t>113206</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6223,12 +6223,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>63,62%</t>
+          <t>63,25%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>75,98%</t>
+          <t>75,89%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>84967</t>
+          <t>84804</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>102459</t>
+          <t>102865</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>60,52%</t>
+          <t>60,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>72,97%</t>
+          <t>73,26%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>184074</t>
+          <t>185031</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>210960</t>
+          <t>210750</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6293,12 +6293,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>63,57%</t>
+          <t>63,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>72,85%</t>
+          <t>72,78%</t>
         </is>
       </c>
     </row>
@@ -6438,12 +6438,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>7142</t>
+          <t>6955</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>16511</t>
+          <t>17289</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6453,12 +6453,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>11499</t>
+          <t>11332</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>23101</t>
+          <t>22973</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>31,85%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>20328</t>
+          <t>20575</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>36040</t>
+          <t>36303</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6523,12 +6523,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,8%</t>
         </is>
       </c>
     </row>
@@ -6551,12 +6551,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2851</t>
+          <t>2817</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>10402</t>
+          <t>10151</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6566,12 +6566,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3767</t>
+          <t>4034</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>12187</t>
+          <t>12554</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6601,12 +6601,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>8388</t>
+          <t>8211</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>19598</t>
+          <t>19135</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6636,12 +6636,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,18%</t>
         </is>
       </c>
     </row>
@@ -6664,12 +6664,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>30835</t>
+          <t>31365</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>42082</t>
+          <t>42053</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6679,12 +6679,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>57,2%</t>
+          <t>58,18%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>78,06%</t>
+          <t>78,0%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>41775</t>
+          <t>41030</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>54325</t>
+          <t>54123</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6714,12 +6714,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>57,92%</t>
+          <t>56,89%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>75,32%</t>
+          <t>75,04%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>75671</t>
+          <t>76677</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>93428</t>
+          <t>93822</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6749,12 +6749,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>60,04%</t>
+          <t>60,84%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>74,13%</t>
+          <t>74,44%</t>
         </is>
       </c>
     </row>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>129000</t>
+          <t>129300</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>163838</t>
+          <t>164242</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>156623</t>
+          <t>158314</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>194353</t>
+          <t>196225</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>295623</t>
+          <t>294609</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>347940</t>
+          <t>347073</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6979,12 +6979,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,16%</t>
         </is>
       </c>
     </row>
@@ -7007,12 +7007,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>44254</t>
+          <t>43338</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>68885</t>
+          <t>64989</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7022,12 +7022,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7042,12 +7042,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>46357</t>
+          <t>46418</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>69878</t>
+          <t>69828</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -7077,12 +7077,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>96712</t>
+          <t>97402</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>129796</t>
+          <t>128641</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7092,12 +7092,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,33%</t>
         </is>
       </c>
     </row>
@@ -7120,12 +7120,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>453133</t>
+          <t>454707</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>492683</t>
+          <t>494357</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7135,12 +7135,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>67,18%</t>
+          <t>67,41%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>73,04%</t>
+          <t>73,29%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7155,12 +7155,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>450290</t>
+          <t>450340</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>492584</t>
+          <t>491052</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7170,12 +7170,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>63,88%</t>
+          <t>63,89%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>69,88%</t>
+          <t>69,66%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7190,12 +7190,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>916301</t>
+          <t>917698</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>973232</t>
+          <t>972996</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7205,12 +7205,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>66,43%</t>
+          <t>66,53%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>70,55%</t>
+          <t>70,54%</t>
         </is>
       </c>
     </row>
@@ -7584,12 +7584,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4034</t>
+          <t>4271</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14592</t>
+          <t>14375</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7599,12 +7599,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7619,12 +7619,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2611</t>
+          <t>2533</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10112</t>
+          <t>10197</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7634,12 +7634,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8846</t>
+          <t>8416</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20922</t>
+          <t>20246</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7669,12 +7669,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,29%</t>
         </is>
       </c>
     </row>
@@ -7697,12 +7697,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>4089</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13374</t>
+          <t>12692</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7712,12 +7712,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5193</t>
+          <t>5359</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15980</t>
+          <t>15598</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7747,12 +7747,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12049</t>
+          <t>11123</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>24529</t>
+          <t>24786</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7782,12 +7782,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,82%</t>
         </is>
       </c>
     </row>
@@ -7810,12 +7810,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>59682</t>
+          <t>59648</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>72061</t>
+          <t>71664</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7825,12 +7825,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>72,36%</t>
+          <t>72,31%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>86,88%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>75535</t>
+          <t>75506</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>87294</t>
+          <t>87007</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7860,12 +7860,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>78,01%</t>
+          <t>77,98%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>138628</t>
+          <t>138453</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>155961</t>
+          <t>156227</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7895,12 +7895,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>77,21%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>87,13%</t>
         </is>
       </c>
     </row>
@@ -8040,12 +8040,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10697</t>
+          <t>10575</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>22960</t>
+          <t>23541</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8055,12 +8055,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>6956</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>17603</t>
+          <t>17711</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8090,12 +8090,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>20234</t>
+          <t>20384</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>37163</t>
+          <t>37253</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,57%</t>
         </is>
       </c>
     </row>
@@ -8153,12 +8153,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4739</t>
+          <t>4797</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14960</t>
+          <t>14174</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8168,12 +8168,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4137</t>
+          <t>4085</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13522</t>
+          <t>12691</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8203,12 +8203,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>10680</t>
+          <t>11062</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>24116</t>
+          <t>24478</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8238,12 +8238,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,54%</t>
         </is>
       </c>
     </row>
@@ -8266,12 +8266,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>68955</t>
+          <t>69616</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>83932</t>
+          <t>83160</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8281,12 +8281,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>67,71%</t>
+          <t>68,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>82,41%</t>
+          <t>81,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>83838</t>
+          <t>84124</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>97213</t>
+          <t>96803</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8316,12 +8316,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>76,05%</t>
+          <t>76,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>88,19%</t>
+          <t>87,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>157785</t>
+          <t>156608</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>177394</t>
+          <t>177147</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8351,12 +8351,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>74,4%</t>
+          <t>73,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>83,64%</t>
+          <t>83,53%</t>
         </is>
       </c>
     </row>
@@ -8496,12 +8496,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6502</t>
+          <t>6540</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16560</t>
+          <t>16509</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8511,12 +8511,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8531,12 +8531,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6947</t>
+          <t>6606</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16635</t>
+          <t>16610</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8546,12 +8546,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8566,12 +8566,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>15686</t>
+          <t>15329</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>29563</t>
+          <t>29120</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8581,12 +8581,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>21,63%</t>
         </is>
       </c>
     </row>
@@ -8609,12 +8609,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3263</t>
+          <t>3569</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11356</t>
+          <t>11158</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8624,12 +8624,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8644,12 +8644,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2776</t>
+          <t>2208</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10063</t>
+          <t>10360</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8679,12 +8679,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7676</t>
+          <t>7535</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18454</t>
+          <t>17689</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8694,12 +8694,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,14%</t>
         </is>
       </c>
     </row>
@@ -8722,12 +8722,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>36784</t>
+          <t>36518</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>48062</t>
+          <t>47714</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8737,12 +8737,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>61,26%</t>
+          <t>60,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,04%</t>
+          <t>79,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8757,12 +8757,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>51982</t>
+          <t>51305</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>63127</t>
+          <t>63383</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8772,12 +8772,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,7%</t>
+          <t>68,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,64%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8792,12 +8792,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>91979</t>
+          <t>92777</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>107824</t>
+          <t>108188</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8807,12 +8807,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,32%</t>
+          <t>68,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,09%</t>
+          <t>80,36%</t>
         </is>
       </c>
     </row>
@@ -8952,12 +8952,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>27834</t>
+          <t>28190</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>45773</t>
+          <t>46310</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8967,12 +8967,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8987,12 +8987,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>25582</t>
+          <t>25873</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>43249</t>
+          <t>43519</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9002,12 +9002,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9022,12 +9022,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>58720</t>
+          <t>58997</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>85517</t>
+          <t>84009</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>19,83%</t>
         </is>
       </c>
     </row>
@@ -9065,12 +9065,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11773</t>
+          <t>11914</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24681</t>
+          <t>24579</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9080,12 +9080,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9100,12 +9100,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9735</t>
+          <t>9333</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>21756</t>
+          <t>21699</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9115,12 +9115,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9135,12 +9135,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>24156</t>
+          <t>24527</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>42679</t>
+          <t>42404</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9150,12 +9150,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,01%</t>
         </is>
       </c>
     </row>
@@ -9178,12 +9178,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>154096</t>
+          <t>154153</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>175062</t>
+          <t>174742</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9193,12 +9193,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>70,25%</t>
+          <t>70,28%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>79,66%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9213,12 +9213,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>145168</t>
+          <t>144966</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>165150</t>
+          <t>165648</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>71,08%</t>
+          <t>70,98%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>80,87%</t>
+          <t>81,11%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9248,12 +9248,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>304729</t>
+          <t>304353</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>334488</t>
+          <t>334189</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9263,12 +9263,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>71,94%</t>
+          <t>71,85%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>78,97%</t>
+          <t>78,9%</t>
         </is>
       </c>
     </row>
@@ -9408,12 +9408,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>14219</t>
+          <t>14538</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>26711</t>
+          <t>27206</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9423,12 +9423,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9443,12 +9443,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>11649</t>
+          <t>11901</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>25245</t>
+          <t>24873</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9458,12 +9458,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9478,12 +9478,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>29708</t>
+          <t>29135</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>49196</t>
+          <t>48782</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9493,12 +9493,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,03%</t>
         </is>
       </c>
     </row>
@@ -9521,12 +9521,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5773</t>
+          <t>6109</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>17111</t>
+          <t>16784</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9536,12 +9536,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9556,12 +9556,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>9300</t>
+          <t>8937</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>21796</t>
+          <t>21979</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9571,12 +9571,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9591,12 +9591,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>18005</t>
+          <t>17424</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>34056</t>
+          <t>34101</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9606,12 +9606,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,61%</t>
         </is>
       </c>
     </row>
@@ -9634,12 +9634,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>91512</t>
+          <t>91170</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>107103</t>
+          <t>106634</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9649,12 +9649,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>70,16%</t>
+          <t>69,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>81,75%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9669,12 +9669,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>99212</t>
+          <t>98597</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>116028</t>
+          <t>115284</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9684,12 +9684,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>70,83%</t>
+          <t>70,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>82,83%</t>
+          <t>82,3%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9704,12 +9704,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>195112</t>
+          <t>195793</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>218510</t>
+          <t>218250</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9719,12 +9719,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>72,12%</t>
+          <t>72,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>80,77%</t>
+          <t>80,68%</t>
         </is>
       </c>
     </row>
@@ -9864,12 +9864,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>7302</t>
+          <t>7025</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>17909</t>
+          <t>17651</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9879,12 +9879,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9899,12 +9899,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>5501</t>
+          <t>5712</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>14893</t>
+          <t>15066</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9914,12 +9914,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9934,12 +9934,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>15896</t>
+          <t>15198</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>30022</t>
+          <t>29361</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9949,12 +9949,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>23,25%</t>
         </is>
       </c>
     </row>
@@ -9977,12 +9977,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1182</t>
+          <t>1226</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7201</t>
+          <t>7790</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9992,12 +9992,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10012,12 +10012,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2952</t>
+          <t>3153</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11280</t>
+          <t>11362</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10027,12 +10027,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10047,12 +10047,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5758</t>
+          <t>5557</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>15093</t>
+          <t>15504</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10062,12 +10062,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,28%</t>
         </is>
       </c>
     </row>
@@ -10090,12 +10090,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>39368</t>
+          <t>39229</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>50359</t>
+          <t>50665</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10105,12 +10105,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>64,45%</t>
+          <t>64,22%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>82,44%</t>
+          <t>82,94%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10125,12 +10125,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>42659</t>
+          <t>43228</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>54575</t>
+          <t>54536</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10140,12 +10140,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>65,44%</t>
+          <t>66,32%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>83,67%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10160,12 +10160,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>85761</t>
+          <t>86795</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>101972</t>
+          <t>102136</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10175,12 +10175,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>67,92%</t>
+          <t>68,74%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>80,89%</t>
         </is>
       </c>
     </row>
@@ -10320,12 +10320,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>89870</t>
+          <t>89669</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>120853</t>
+          <t>118788</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10335,12 +10335,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10355,12 +10355,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>75271</t>
+          <t>74645</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>105534</t>
+          <t>102074</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10370,12 +10370,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10390,12 +10390,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>173041</t>
+          <t>173512</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>212486</t>
+          <t>215272</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10405,12 +10405,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,99%</t>
         </is>
       </c>
     </row>
@@ -10433,12 +10433,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>44873</t>
+          <t>43820</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>68562</t>
+          <t>67573</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10448,12 +10448,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10468,12 +10468,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>46104</t>
+          <t>47244</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>70951</t>
+          <t>70593</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10483,12 +10483,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10503,12 +10503,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>96068</t>
+          <t>98694</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>128104</t>
+          <t>131089</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10518,12 +10518,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,74%</t>
         </is>
       </c>
     </row>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>478121</t>
+          <t>477341</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>512095</t>
+          <t>513494</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10561,12 +10561,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>72,97%</t>
+          <t>72,85%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>78,15%</t>
+          <t>78,37%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10581,12 +10581,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>524732</t>
+          <t>526834</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>563133</t>
+          <t>562505</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10596,12 +10596,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>75,92%</t>
+          <t>76,23%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>81,48%</t>
+          <t>81,39%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10616,12 +10616,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1016270</t>
+          <t>1015899</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1066510</t>
+          <t>1065359</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10631,12 +10631,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>75,48%</t>
+          <t>75,45%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>79,21%</t>
+          <t>79,13%</t>
         </is>
       </c>
     </row>
